--- a/artfynd/A 52150-2025 artfynd.xlsx
+++ b/artfynd/A 52150-2025 artfynd.xlsx
@@ -1030,7 +1030,7 @@
         <v>89789170</v>
       </c>
       <c r="B5" t="n">
-        <v>58592</v>
+        <v>58647</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 52150-2025 artfynd.xlsx
+++ b/artfynd/A 52150-2025 artfynd.xlsx
@@ -1030,7 +1030,7 @@
         <v>89789170</v>
       </c>
       <c r="B5" t="n">
-        <v>58647</v>
+        <v>58660</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 52150-2025 artfynd.xlsx
+++ b/artfynd/A 52150-2025 artfynd.xlsx
@@ -1030,7 +1030,7 @@
         <v>89789170</v>
       </c>
       <c r="B5" t="n">
-        <v>58660</v>
+        <v>58662</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 52150-2025 artfynd.xlsx
+++ b/artfynd/A 52150-2025 artfynd.xlsx
@@ -1062,11 +1062,7 @@
       </c>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+      <c r="M5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>

--- a/artfynd/A 52150-2025 artfynd.xlsx
+++ b/artfynd/A 52150-2025 artfynd.xlsx
@@ -1030,7 +1030,7 @@
         <v>89789170</v>
       </c>
       <c r="B5" t="n">
-        <v>58662</v>
+        <v>58672</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 52150-2025 artfynd.xlsx
+++ b/artfynd/A 52150-2025 artfynd.xlsx
@@ -1030,7 +1030,7 @@
         <v>89789170</v>
       </c>
       <c r="B5" t="n">
-        <v>58672</v>
+        <v>58674</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 52150-2025 artfynd.xlsx
+++ b/artfynd/A 52150-2025 artfynd.xlsx
@@ -1030,7 +1030,7 @@
         <v>89789170</v>
       </c>
       <c r="B5" t="n">
-        <v>58674</v>
+        <v>58676</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 52150-2025 artfynd.xlsx
+++ b/artfynd/A 52150-2025 artfynd.xlsx
@@ -1030,7 +1030,7 @@
         <v>89789170</v>
       </c>
       <c r="B5" t="n">
-        <v>58676</v>
+        <v>58679</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
